--- a/public/data/contract_fuel.xlsx
+++ b/public/data/contract_fuel.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,13 +424,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>89292bb5-bc96-433f-88b4-e7ff30967b31</v>
+        <v>74b1ee3f-d701-4a98-a6ae-0e0d0e79a09d</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D2" t="str">
         <v>CTR-001-001</v>
@@ -447,145 +447,398 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>a4d6438a-e750-482a-aa81-64714fb29e09</v>
+        <v>204bcafa-e56d-4ec0-9ea0-19998ba6d019</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D3" t="str">
-        <v>CTR-002-001</v>
+        <v>CTR-001-002</v>
       </c>
       <c r="E3" t="str">
         <v>Fuel surcharge</v>
       </c>
       <c r="F3" t="str">
-        <v>Included</v>
+        <v>$48 per flight hour</v>
       </c>
       <c r="G3" t="str">
-        <v>Bundled into fare</v>
+        <v>Charter fuel variable</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>8b7967fc-4dc3-4d13-8f38-2117aa3d04bd</v>
+        <v>1089e4c1-7022-4470-86fc-0a67ee7c461e</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D4" t="str">
-        <v>CTR-003-001</v>
+        <v>CTR-002-001</v>
       </c>
       <c r="E4" t="str">
         <v>Fuel surcharge</v>
       </c>
       <c r="F4" t="str">
-        <v>$45 per flight hour</v>
+        <v>Included</v>
       </c>
       <c r="G4" t="str">
-        <v>Variable based on Platts index</v>
+        <v>Bundled into fare</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>a06a1d7f-d258-46a2-b182-5cf06c1d0643</v>
+        <v>0bb869a3-7727-4d7f-922d-893fb8abf2a5</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D5" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-001</v>
       </c>
       <c r="E5" t="str">
         <v>Fuel surcharge</v>
       </c>
       <c r="F5" t="str">
-        <v>Included</v>
+        <v>$45 per flight hour</v>
       </c>
       <c r="G5" t="str">
-        <v>Bundled into transfer fare</v>
+        <v>Variable based on Platts index</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>c94e4ba7-5496-4162-93f3-bbb8c782d64c</v>
+        <v>03aef89d-d7a0-4a22-9766-a623e8b6bf10</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D6" t="str">
-        <v>CTR-008-001</v>
+        <v>CTR-003-002</v>
       </c>
       <c r="E6" t="str">
         <v>Fuel surcharge</v>
       </c>
       <c r="F6" t="str">
-        <v>$50 per flight hour</v>
+        <v>Included</v>
       </c>
       <c r="G6" t="str">
-        <v>Reviewed quarterly</v>
+        <v>Bundled into fare</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>09743961-7db3-48ce-8496-7400ef15e0e2</v>
+        <v>960f97d2-de98-407b-96af-2a0683bbc331</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D7" t="str">
-        <v>CTR-009-001</v>
+        <v>CTR-003-003</v>
       </c>
       <c r="E7" t="str">
         <v>Fuel surcharge</v>
       </c>
       <c r="F7" t="str">
-        <v>$15 per trip</v>
+        <v>$52 per flight hour</v>
       </c>
       <c r="G7" t="str">
-        <v>Speedboat fuel levy</v>
+        <v>Signed charter premium rate</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>4dcfcb63-0916-4cd1-90e0-b2d42e6a763c</v>
+        <v>11ac1ad7-235f-4bc1-9222-12b1233ee62a</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D8" t="str">
+        <v>CTR-005-001</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Fuel surcharge</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Included</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Bundled</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>706cc27b-e553-4e5c-a8de-e487dcb4b7ce</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C9" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D9" t="str">
+        <v>CTR-005-002</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Fuel surcharge</v>
+      </c>
+      <c r="F9" t="str">
+        <v>$46 per flight hour</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Charter rate</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>c46f568a-9c45-4cd4-b099-399f08076fef</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C10" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D10" t="str">
+        <v>CTR-006-001</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Fuel surcharge</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Included</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Bundled into transfer fare</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>0a975d17-0dc0-4cac-b2c9-897e6a98617b</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C11" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D11" t="str">
+        <v>CTR-006-002</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Fuel surcharge</v>
+      </c>
+      <c r="F11" t="str">
+        <v>$47 per flight hour</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Charter fuel</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3f62f105-444e-4141-9f53-82a68a866a1d</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C12" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D12" t="str">
+        <v>CTR-006-003</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Fuel surcharge</v>
+      </c>
+      <c r="F12" t="str">
+        <v>$55 per flight hour</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Signed charter premium</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>25d63e04-62d1-489e-9904-7c6babb8294b</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C13" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D13" t="str">
+        <v>CTR-007-001</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Fuel surcharge</v>
+      </c>
+      <c r="F13" t="str">
+        <v>$15 per trip</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Speedboat fuel levy</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>f4b4224c-dfd8-4b31-86e1-1c1474d4bacf</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C14" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D14" t="str">
+        <v>CTR-007-002</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Fuel surcharge</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Included</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Seaplane fare inclusive</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>1cbf07e1-81a2-4423-bb0b-f7200f251cf2</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C15" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D15" t="str">
+        <v>CTR-008-001</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Fuel surcharge</v>
+      </c>
+      <c r="F15" t="str">
+        <v>$50 per flight hour</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Reviewed quarterly</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5c253bd0-25b4-4396-aada-cf895f99e546</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C16" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D16" t="str">
+        <v>CTR-008-002</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Fuel surcharge</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Included</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Bundled</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2c2f5f06-31b2-4693-b44f-b2bf3f8aa74d</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C17" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D17" t="str">
+        <v>CTR-009-001</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Fuel surcharge</v>
+      </c>
+      <c r="F17" t="str">
+        <v>$15 per trip</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Speedboat fuel levy</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>a395032e-bfc2-421b-b7bd-94c678845e80</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C18" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D18" t="str">
         <v>CTR-010-001</v>
       </c>
-      <c r="E8" t="str">
-        <v>Fuel surcharge</v>
-      </c>
-      <c r="F8" t="str">
+      <c r="E18" t="str">
+        <v>Fuel surcharge</v>
+      </c>
+      <c r="F18" t="str">
         <v>$40 per flight hour</v>
       </c>
-      <c r="G8" t="str">
+      <c r="G18" t="str">
         <v>Based on Platts Singapore</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>fe4112a8-16a8-42d1-9243-37c68d1b50bf</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C19" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D19" t="str">
+        <v>CTR-010-002</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Fuel surcharge</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Included</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Bundled</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G19"/>
   </ignoredErrors>
 </worksheet>
 </file>